--- a/example.xlsx
+++ b/example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yjkong\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yjkong\Documents\NetSarang Computer\8\Xftp\Temporary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8E32ED-70C0-45A1-92E4-ABC46CF31975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CA2F7D-29AC-411E-88B9-5D54A151CD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8D2F1E5D-5195-4282-9BFC-A577C7BA9876}"/>
+    <workbookView xWindow="3040" yWindow="2850" windowWidth="14140" windowHeight="13150" xr2:uid="{8D2F1E5D-5195-4282-9BFC-A577C7BA9876}"/>
   </bookViews>
   <sheets>
     <sheet name="example" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>SMILES</t>
   </si>
@@ -29,6 +29,10 @@
   </si>
   <si>
     <t>C1C=CC=CC=1</t>
+  </si>
+  <si>
+    <t>ClC1=C(O)C(C(OC)=O)=C(Cl)C=C1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1002,6 +1006,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4358680-2B32-4008-81CE-EE03A5B11D8A}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1021,7 +1028,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>2</v>
